--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][CI]Aggregated_U_test.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][CI]Aggregated_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mean_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Mean_P2</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>SD_P1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>SD_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Median_P1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Median_P2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Median_difference_P2_minus_P1</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -498,37 +510,37 @@
         <v>930</v>
       </c>
       <c r="C2" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="D2" t="n">
-        <v>8.923628794285092</v>
+        <v>8.786179411849368</v>
       </c>
       <c r="E2" t="n">
-        <v>13.92649684122195</v>
+        <v>13.71581597203818</v>
       </c>
       <c r="F2" t="n">
-        <v>4.06152816874354</v>
+        <v>4.07471405877288</v>
       </c>
       <c r="G2" t="n">
-        <v>3.324225829704444</v>
+        <v>3.315378195274013</v>
       </c>
       <c r="H2" t="n">
-        <v>9.134368180346044</v>
+        <v>8.991164804000764</v>
       </c>
       <c r="I2" t="n">
-        <v>13.9755917585467</v>
+        <v>13.7443469830019</v>
       </c>
       <c r="J2" t="n">
-        <v>4.841223578200655</v>
+        <v>4.753182179001136</v>
       </c>
       <c r="K2" t="n">
-        <v>98852</v>
+        <v>90821</v>
       </c>
       <c r="L2" t="n">
-        <v>3.833144748124343e-101</v>
+        <v>9.470841706484966e-93</v>
       </c>
       <c r="M2" t="n">
-        <v>1.533257899249737e-100</v>
+        <v>3.788336682593986e-92</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -544,37 +556,37 @@
         <v>930</v>
       </c>
       <c r="C3" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="D3" t="n">
-        <v>70.62618549015373</v>
+        <v>70.54901398337343</v>
       </c>
       <c r="E3" t="n">
-        <v>79.12919862757822</v>
+        <v>79.24245593211478</v>
       </c>
       <c r="F3" t="n">
-        <v>11.07783003082875</v>
+        <v>11.04969754104021</v>
       </c>
       <c r="G3" t="n">
-        <v>7.224019472417474</v>
+        <v>7.289128565945613</v>
       </c>
       <c r="H3" t="n">
-        <v>71.08776883415381</v>
+        <v>71.00838342147301</v>
       </c>
       <c r="I3" t="n">
-        <v>78.70443585060696</v>
+        <v>78.77494340110115</v>
       </c>
       <c r="J3" t="n">
-        <v>7.61666701645315</v>
+        <v>7.766559979628141</v>
       </c>
       <c r="K3" t="n">
-        <v>153532</v>
+        <v>135597</v>
       </c>
       <c r="L3" t="n">
-        <v>5.144982850016331e-50</v>
+        <v>4.726183947756198e-49</v>
       </c>
       <c r="M3" t="n">
-        <v>2.057993140006533e-49</v>
+        <v>1.890473579102479e-48</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -590,37 +602,37 @@
         <v>930</v>
       </c>
       <c r="C4" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="D4" t="n">
-        <v>11.39348025290619</v>
+        <v>11.21297277068996</v>
       </c>
       <c r="E4" t="n">
-        <v>16.64276307683903</v>
+        <v>16.43253553973835</v>
       </c>
       <c r="F4" t="n">
-        <v>3.831560851818865</v>
+        <v>3.836043256128496</v>
       </c>
       <c r="G4" t="n">
-        <v>3.361224239375245</v>
+        <v>3.369562462026316</v>
       </c>
       <c r="H4" t="n">
-        <v>11.46561644925975</v>
+        <v>11.22376273259095</v>
       </c>
       <c r="I4" t="n">
-        <v>16.81150970433</v>
+        <v>16.53662357589805</v>
       </c>
       <c r="J4" t="n">
-        <v>5.34589325507025</v>
+        <v>5.312860843307099</v>
       </c>
       <c r="K4" t="n">
-        <v>88568</v>
+        <v>80837</v>
       </c>
       <c r="L4" t="n">
-        <v>8.613584817751495e-113</v>
+        <v>2.040058440905503e-104</v>
       </c>
       <c r="M4" t="n">
-        <v>3.445433927100598e-112</v>
+        <v>8.160233763622012e-104</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -636,37 +648,37 @@
         <v>930</v>
       </c>
       <c r="C5" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="D5" t="n">
-        <v>96.20493489488085</v>
+        <v>96.43118998018885</v>
       </c>
       <c r="E5" t="n">
-        <v>80.11119527245044</v>
+        <v>80.80197911631667</v>
       </c>
       <c r="F5" t="n">
-        <v>25.44113069496144</v>
+        <v>25.35490069838508</v>
       </c>
       <c r="G5" t="n">
-        <v>30.07520053609668</v>
+        <v>30.58907381966574</v>
       </c>
       <c r="H5" t="n">
-        <v>100.177947889222</v>
+        <v>100.0061232461241</v>
       </c>
       <c r="I5" t="n">
-        <v>82.8402127626983</v>
+        <v>83.10362110164814</v>
       </c>
       <c r="J5" t="n">
-        <v>-17.3377351265237</v>
+        <v>-16.902502144476</v>
       </c>
       <c r="K5" t="n">
-        <v>366509</v>
+        <v>326166</v>
       </c>
       <c r="L5" t="n">
-        <v>3.346882008576464e-25</v>
+        <v>1.098058981270254e-21</v>
       </c>
       <c r="M5" t="n">
-        <v>1.338752803430586e-24</v>
+        <v>4.392235925081015e-21</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
